--- a/ewatch_data/target_vs_actual_monthly.xlsx
+++ b/ewatch_data/target_vs_actual_monthly.xlsx
@@ -470,7 +470,7 @@
   <pageSetup orientation="portrait" r:id="rId1"/>
   <headerFooter>
     <oddFooter>&amp;LNote : Blank column/s = data unavailable 
- Printed Date : 05/06/2026 06:32:59 PM</oddFooter>
+ Printed Date : 09/06/2026 01:42:25 PM</oddFooter>
   </headerFooter>
 </worksheet>
 </file>